--- a/ig/nr-correct-url/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/ig/nr-correct-url/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-16T08:30:34+00:00</t>
+    <t>2024-04-16T10:01:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
